--- a/compare/output/dscale_GreenElec_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_GreenElec_downscaled_SSP245.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1475.82846</v>
+        <v>1475.915393</v>
       </c>
       <c r="F2" t="n">
-        <v>3491.779114</v>
+        <v>3492.293688</v>
       </c>
       <c r="G2" t="n">
-        <v>7148.302849</v>
+        <v>7150.450666</v>
       </c>
       <c r="H2" t="n">
-        <v>12222.775409</v>
+        <v>12230.437905</v>
       </c>
       <c r="I2" t="n">
-        <v>18620.000964</v>
+        <v>18650.635285</v>
       </c>
       <c r="J2" t="n">
         <v>15569.824319</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>125.817656</v>
+        <v>125.80868</v>
       </c>
       <c r="F3" t="n">
-        <v>266.536617</v>
+        <v>266.487654</v>
       </c>
       <c r="G3" t="n">
-        <v>512.189071</v>
+        <v>511.991888</v>
       </c>
       <c r="H3" t="n">
-        <v>857.008562</v>
+        <v>856.324137</v>
       </c>
       <c r="I3" t="n">
-        <v>1322.855296</v>
+        <v>1320.124307</v>
       </c>
       <c r="J3" t="n">
         <v>3353.56188</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>148.295154</v>
+        <v>148.232613</v>
       </c>
       <c r="F4" t="n">
-        <v>278.231964</v>
+        <v>277.942925</v>
       </c>
       <c r="G4" t="n">
-        <v>461.142868</v>
+        <v>460.199398</v>
       </c>
       <c r="H4" t="n">
-        <v>692.810367</v>
+        <v>689.983688</v>
       </c>
       <c r="I4" t="n">
-        <v>994.7048160000001</v>
+        <v>984.5564450000001</v>
       </c>
       <c r="J4" t="n">
         <v>5574.07205</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>78.329202</v>
+        <v>78.226682</v>
       </c>
       <c r="F5" t="n">
-        <v>217.280394</v>
+        <v>216.491043</v>
       </c>
       <c r="G5" t="n">
-        <v>567.635932</v>
+        <v>562.958061</v>
       </c>
       <c r="H5" t="n">
-        <v>1200.04917</v>
+        <v>1178.435972</v>
       </c>
       <c r="I5" t="n">
-        <v>2206.360261</v>
+        <v>2104.827231</v>
       </c>
       <c r="J5" t="n">
         <v>51400.11258</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>37124.960427</v>
+        <v>37126.877813</v>
       </c>
       <c r="F6" t="n">
-        <v>86608.35649999999</v>
+        <v>86619.45288500001</v>
       </c>
       <c r="G6" t="n">
-        <v>161137.950034</v>
+        <v>161181.714936</v>
       </c>
       <c r="H6" t="n">
-        <v>256671.136088</v>
+        <v>256821.39226</v>
       </c>
       <c r="I6" t="n">
-        <v>380475.719435</v>
+        <v>381067.864952</v>
       </c>
       <c r="J6" t="n">
         <v>332563.527282</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29573.050952</v>
+        <v>29574.426671</v>
       </c>
       <c r="F7" t="n">
-        <v>72950.93002099999</v>
+        <v>72959.01906000001</v>
       </c>
       <c r="G7" t="n">
-        <v>161785.573454</v>
+        <v>161819.751882</v>
       </c>
       <c r="H7" t="n">
-        <v>303582.934806</v>
+        <v>303708.131968</v>
       </c>
       <c r="I7" t="n">
-        <v>510025.935912</v>
+        <v>510542.991364</v>
       </c>
       <c r="J7" t="n">
         <v>632986.378396</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3382.352236</v>
+        <v>3382.184833</v>
       </c>
       <c r="F8" t="n">
-        <v>7866.654239</v>
+        <v>7865.583201</v>
       </c>
       <c r="G8" t="n">
-        <v>16103.552366</v>
+        <v>16098.802366</v>
       </c>
       <c r="H8" t="n">
-        <v>28031.967179</v>
+        <v>28014.649236</v>
       </c>
       <c r="I8" t="n">
-        <v>44123.457681</v>
+        <v>44053.29549</v>
       </c>
       <c r="J8" t="n">
         <v>100726.087807</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2420.331208</v>
+        <v>2419.727472</v>
       </c>
       <c r="F9" t="n">
-        <v>4413.576432</v>
+        <v>4410.852236</v>
       </c>
       <c r="G9" t="n">
-        <v>6923.990857</v>
+        <v>6915.68626</v>
       </c>
       <c r="H9" t="n">
-        <v>9693.144996000001</v>
+        <v>9670.460675</v>
       </c>
       <c r="I9" t="n">
-        <v>12976.74297</v>
+        <v>12902.045926</v>
       </c>
       <c r="J9" t="n">
         <v>46759.271758</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1073.508216</v>
+        <v>1073.13632</v>
       </c>
       <c r="F10" t="n">
-        <v>2295.887509</v>
+        <v>2293.859587</v>
       </c>
       <c r="G10" t="n">
-        <v>4126.532799</v>
+        <v>4119.240195</v>
       </c>
       <c r="H10" t="n">
-        <v>6557.790321</v>
+        <v>6534.523851</v>
       </c>
       <c r="I10" t="n">
-        <v>9764.353015999999</v>
+        <v>9677.786641999999</v>
       </c>
       <c r="J10" t="n">
         <v>51047.989438</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29965.563919</v>
+        <v>29963.794201</v>
       </c>
       <c r="F11" t="n">
-        <v>68093.59649</v>
+        <v>68082.64068</v>
       </c>
       <c r="G11" t="n">
-        <v>136256.293826</v>
+        <v>136209.115492</v>
       </c>
       <c r="H11" t="n">
-        <v>236003.415069</v>
+        <v>235830.169621</v>
       </c>
       <c r="I11" t="n">
-        <v>371404.685647</v>
+        <v>370691.716026</v>
       </c>
       <c r="J11" t="n">
         <v>896550.586015</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1574.861435</v>
+        <v>1574.920486</v>
       </c>
       <c r="F12" t="n">
-        <v>3714.006854</v>
+        <v>3714.335832</v>
       </c>
       <c r="G12" t="n">
-        <v>7837.853563</v>
+        <v>7839.176274</v>
       </c>
       <c r="H12" t="n">
-        <v>14089.867836</v>
+        <v>14094.556593</v>
       </c>
       <c r="I12" t="n">
-        <v>22638.505504</v>
+        <v>22657.383598</v>
       </c>
       <c r="J12" t="n">
         <v>28919.258778</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12299.678135</v>
+        <v>12299.325838</v>
       </c>
       <c r="F13" t="n">
-        <v>28043.334136</v>
+        <v>28041.211477</v>
       </c>
       <c r="G13" t="n">
-        <v>54700.551281</v>
+        <v>54692.48148</v>
       </c>
       <c r="H13" t="n">
-        <v>93162.434096</v>
+        <v>93136.267995</v>
       </c>
       <c r="I13" t="n">
-        <v>147309.709398</v>
+        <v>147209.803633</v>
       </c>
       <c r="J13" t="n">
         <v>284534.130596</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>800.124695</v>
+        <v>800.055884</v>
       </c>
       <c r="F14" t="n">
-        <v>1659.242056</v>
+        <v>1658.867446</v>
       </c>
       <c r="G14" t="n">
-        <v>3803.063411</v>
+        <v>3801.203429</v>
       </c>
       <c r="H14" t="n">
-        <v>6496.878118</v>
+        <v>6489.811051</v>
       </c>
       <c r="I14" t="n">
-        <v>9598.839610999999</v>
+        <v>9569.476119999999</v>
       </c>
       <c r="J14" t="n">
         <v>322854.217583</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>56958.074601</v>
+        <v>56958.202403</v>
       </c>
       <c r="F15" t="n">
-        <v>129113.902368</v>
+        <v>129114.518386</v>
       </c>
       <c r="G15" t="n">
-        <v>306881.807245</v>
+        <v>306884.443537</v>
       </c>
       <c r="H15" t="n">
-        <v>530785.367529</v>
+        <v>530794.416794</v>
       </c>
       <c r="I15" t="n">
-        <v>783942.720219</v>
+        <v>783978.279985</v>
       </c>
       <c r="J15" t="n">
         <v>762031.417787</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29.001501</v>
+        <v>28.908717</v>
       </c>
       <c r="F16" t="n">
-        <v>52.503132</v>
+        <v>52.119742</v>
       </c>
       <c r="G16" t="n">
-        <v>101.946834</v>
+        <v>100.583765</v>
       </c>
       <c r="H16" t="n">
-        <v>155.181635</v>
+        <v>151.201129</v>
       </c>
       <c r="I16" t="n">
-        <v>223.824123</v>
+        <v>210.043418</v>
       </c>
       <c r="J16" t="n">
         <v>129485.114282</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>15888.123936</v>
+        <v>15888.175348</v>
       </c>
       <c r="F17" t="n">
-        <v>33233.658961</v>
+        <v>33233.914759</v>
       </c>
       <c r="G17" t="n">
-        <v>74241.011226</v>
+        <v>74242.14365300001</v>
       </c>
       <c r="H17" t="n">
-        <v>121818.306216</v>
+        <v>121822.221083</v>
       </c>
       <c r="I17" t="n">
-        <v>171970.881087</v>
+        <v>171986.003463</v>
       </c>
       <c r="J17" t="n">
         <v>86578.575919</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1992.615202</v>
+        <v>1992.597582</v>
       </c>
       <c r="F18" t="n">
-        <v>4359.208493</v>
+        <v>4359.094678</v>
       </c>
       <c r="G18" t="n">
-        <v>9642.654924</v>
+        <v>9642.109256</v>
       </c>
       <c r="H18" t="n">
-        <v>15644.034043</v>
+        <v>15642.117483</v>
       </c>
       <c r="I18" t="n">
-        <v>22183.1874</v>
+        <v>22175.649456</v>
       </c>
       <c r="J18" t="n">
         <v>110822.27887</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18779.918889</v>
+        <v>18779.704606</v>
       </c>
       <c r="F19" t="n">
-        <v>25367.232122</v>
+        <v>25366.477938</v>
       </c>
       <c r="G19" t="n">
-        <v>33657.545332</v>
+        <v>33655.471017</v>
       </c>
       <c r="H19" t="n">
-        <v>43908.84081</v>
+        <v>43903.225842</v>
       </c>
       <c r="I19" t="n">
-        <v>57523.797572</v>
+        <v>57504.738814</v>
       </c>
       <c r="J19" t="n">
         <v>327731.687591</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.914697</v>
+        <v>11.843367</v>
       </c>
       <c r="F20" t="n">
-        <v>18.023767</v>
+        <v>17.781007</v>
       </c>
       <c r="G20" t="n">
-        <v>30.761857</v>
+        <v>30.065289</v>
       </c>
       <c r="H20" t="n">
-        <v>58.057057</v>
+        <v>56.12827</v>
       </c>
       <c r="I20" t="n">
-        <v>145.250357</v>
+        <v>138.738727</v>
       </c>
       <c r="J20" t="n">
         <v>80261.706833</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>348.453487</v>
+        <v>348.449388</v>
       </c>
       <c r="F21" t="n">
-        <v>381.143277</v>
+        <v>381.132122</v>
       </c>
       <c r="G21" t="n">
-        <v>436.786857</v>
+        <v>436.760961</v>
       </c>
       <c r="H21" t="n">
-        <v>524.166196</v>
+        <v>524.1017430000001</v>
       </c>
       <c r="I21" t="n">
-        <v>657.718947</v>
+        <v>657.506619</v>
       </c>
       <c r="J21" t="n">
         <v>3626.242588</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>61265.008446</v>
+        <v>61265.231127</v>
       </c>
       <c r="F22" t="n">
-        <v>83614.223933</v>
+        <v>83615.00835400001</v>
       </c>
       <c r="G22" t="n">
-        <v>111744.522703</v>
+        <v>111746.657698</v>
       </c>
       <c r="H22" t="n">
-        <v>145410.43807</v>
+        <v>145416.059985</v>
       </c>
       <c r="I22" t="n">
-        <v>188981.493437</v>
+        <v>188999.879454</v>
       </c>
       <c r="J22" t="n">
         <v>51137.969749</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2652.897913</v>
+        <v>2652.888818</v>
       </c>
       <c r="F23" t="n">
-        <v>3812.65852</v>
+        <v>3812.62311</v>
       </c>
       <c r="G23" t="n">
-        <v>5498.668039</v>
+        <v>5498.556524</v>
       </c>
       <c r="H23" t="n">
-        <v>7887.492451</v>
+        <v>7887.141221</v>
       </c>
       <c r="I23" t="n">
-        <v>11346.92008</v>
+        <v>11345.536576</v>
       </c>
       <c r="J23" t="n">
         <v>38335.451194</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5392.28616</v>
+        <v>5392.273252</v>
       </c>
       <c r="F24" t="n">
-        <v>6864.445913</v>
+        <v>6864.402429</v>
       </c>
       <c r="G24" t="n">
-        <v>8946.235768</v>
+        <v>8946.112127</v>
       </c>
       <c r="H24" t="n">
-        <v>11446.949396</v>
+        <v>11446.60401</v>
       </c>
       <c r="I24" t="n">
-        <v>14579.562422</v>
+        <v>14578.369001</v>
       </c>
       <c r="J24" t="n">
         <v>36050.64666</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1291.208493</v>
+        <v>1291.202672</v>
       </c>
       <c r="F25" t="n">
-        <v>1517.639187</v>
+        <v>1517.621819</v>
       </c>
       <c r="G25" t="n">
-        <v>1867.096133</v>
+        <v>1867.051356</v>
       </c>
       <c r="H25" t="n">
-        <v>2361.76099</v>
+        <v>2361.639243</v>
       </c>
       <c r="I25" t="n">
-        <v>3050.34202</v>
+        <v>3049.916279</v>
       </c>
       <c r="J25" t="n">
         <v>9963.479331</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7808.953997</v>
+        <v>7808.848109</v>
       </c>
       <c r="F26" t="n">
-        <v>10107.335917</v>
+        <v>10106.98355</v>
       </c>
       <c r="G26" t="n">
-        <v>12612.328832</v>
+        <v>12611.436872</v>
       </c>
       <c r="H26" t="n">
-        <v>15556.919676</v>
+        <v>15554.686029</v>
       </c>
       <c r="I26" t="n">
-        <v>19430.882117</v>
+        <v>19423.801542</v>
       </c>
       <c r="J26" t="n">
         <v>112684.870198</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>46595.071544</v>
+        <v>46595.194891</v>
       </c>
       <c r="F27" t="n">
-        <v>62612.545378</v>
+        <v>62612.97307</v>
       </c>
       <c r="G27" t="n">
-        <v>80823.889893</v>
+        <v>80825.01679199999</v>
       </c>
       <c r="H27" t="n">
-        <v>103907.131538</v>
+        <v>103910.056316</v>
       </c>
       <c r="I27" t="n">
-        <v>136237.708073</v>
+        <v>136247.280758</v>
       </c>
       <c r="J27" t="n">
         <v>84926.484333</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18202.190674</v>
+        <v>18202.268071</v>
       </c>
       <c r="F28" t="n">
-        <v>22208.221626</v>
+        <v>22208.466241</v>
       </c>
       <c r="G28" t="n">
-        <v>31403.461533</v>
+        <v>31404.168309</v>
       </c>
       <c r="H28" t="n">
-        <v>46258.867991</v>
+        <v>46260.981516</v>
       </c>
       <c r="I28" t="n">
-        <v>68512.122051</v>
+        <v>68520.029306</v>
       </c>
       <c r="J28" t="n">
         <v>3181.654998</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22.275431</v>
+        <v>22.266438</v>
       </c>
       <c r="F29" t="n">
-        <v>31.105146</v>
+        <v>31.072705</v>
       </c>
       <c r="G29" t="n">
-        <v>44.672992</v>
+        <v>44.574635</v>
       </c>
       <c r="H29" t="n">
-        <v>63.670763</v>
+        <v>63.374049</v>
       </c>
       <c r="I29" t="n">
-        <v>92.193528</v>
+        <v>91.06971900000001</v>
       </c>
       <c r="J29" t="n">
         <v>10079.425785</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>411.675365</v>
+        <v>411.66782</v>
       </c>
       <c r="F30" t="n">
-        <v>535.8649789999999</v>
+        <v>535.840542</v>
       </c>
       <c r="G30" t="n">
-        <v>721.820659</v>
+        <v>721.750754</v>
       </c>
       <c r="H30" t="n">
-        <v>999.199648</v>
+        <v>998.990179</v>
       </c>
       <c r="I30" t="n">
-        <v>1389.628782</v>
+        <v>1388.853117</v>
       </c>
       <c r="J30" t="n">
         <v>8791.542563999999</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>769.9626500000001</v>
+        <v>769.966799</v>
       </c>
       <c r="F31" t="n">
-        <v>1099.332547</v>
+        <v>1099.346672</v>
       </c>
       <c r="G31" t="n">
-        <v>1536.701976</v>
+        <v>1536.734841</v>
       </c>
       <c r="H31" t="n">
-        <v>2137.346937</v>
+        <v>2137.423929</v>
       </c>
       <c r="I31" t="n">
-        <v>2987.521569</v>
+        <v>2987.766651</v>
       </c>
       <c r="J31" t="n">
         <v>2381.915563</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5403.388921</v>
+        <v>5403.40853</v>
       </c>
       <c r="F32" t="n">
-        <v>6903.597756</v>
+        <v>6903.658328</v>
       </c>
       <c r="G32" t="n">
-        <v>9082.295677</v>
+        <v>9082.416841</v>
       </c>
       <c r="H32" t="n">
-        <v>12296.282903</v>
+        <v>12296.519084</v>
       </c>
       <c r="I32" t="n">
-        <v>17281.157692</v>
+        <v>17281.775849</v>
       </c>
       <c r="J32" t="n">
         <v>21750.118884</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>16295.383904</v>
+        <v>16295.473288</v>
       </c>
       <c r="F33" t="n">
-        <v>22653.68259</v>
+        <v>22653.981944</v>
       </c>
       <c r="G33" t="n">
-        <v>32233.43587</v>
+        <v>32234.145026</v>
       </c>
       <c r="H33" t="n">
-        <v>45608.195793</v>
+        <v>45609.883738</v>
       </c>
       <c r="I33" t="n">
-        <v>64744.642345</v>
+        <v>64750.079112</v>
       </c>
       <c r="J33" t="n">
         <v>51129.007544</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>33150.564503</v>
+        <v>33150.820018</v>
       </c>
       <c r="F34" t="n">
-        <v>80912.458698</v>
+        <v>80913.971168</v>
       </c>
       <c r="G34" t="n">
-        <v>195140.067456</v>
+        <v>195146.464176</v>
       </c>
       <c r="H34" t="n">
-        <v>399129.968548</v>
+        <v>399153.316472</v>
       </c>
       <c r="I34" t="n">
-        <v>716332.949751</v>
+        <v>716432.276833</v>
       </c>
       <c r="J34" t="n">
         <v>263736.161607</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4072.003204</v>
+        <v>4072.02119</v>
       </c>
       <c r="F35" t="n">
-        <v>6991.185036</v>
+        <v>6991.250273</v>
       </c>
       <c r="G35" t="n">
-        <v>11980.06256</v>
+        <v>11980.199817</v>
       </c>
       <c r="H35" t="n">
-        <v>18787.443037</v>
+        <v>18787.661387</v>
       </c>
       <c r="I35" t="n">
-        <v>27604.070564</v>
+        <v>27604.449535</v>
       </c>
       <c r="J35" t="n">
         <v>38336.740776</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>82.42721</v>
+        <v>82.423624</v>
       </c>
       <c r="F36" t="n">
-        <v>113.912604</v>
+        <v>113.898989</v>
       </c>
       <c r="G36" t="n">
-        <v>143.087427</v>
+        <v>143.0515</v>
       </c>
       <c r="H36" t="n">
-        <v>173.816623</v>
+        <v>173.726472</v>
       </c>
       <c r="I36" t="n">
-        <v>213.853674</v>
+        <v>213.568119</v>
       </c>
       <c r="J36" t="n">
         <v>2453.378945</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4535.639585</v>
+        <v>4535.634709</v>
       </c>
       <c r="F37" t="n">
-        <v>5604.327406</v>
+        <v>5604.311952</v>
       </c>
       <c r="G37" t="n">
-        <v>7050.357691</v>
+        <v>7050.291199</v>
       </c>
       <c r="H37" t="n">
-        <v>9004.956832</v>
+        <v>9004.720289000001</v>
       </c>
       <c r="I37" t="n">
-        <v>11783.504602</v>
+        <v>11782.583228</v>
       </c>
       <c r="J37" t="n">
         <v>23991.534687</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>21687.559384</v>
+        <v>21687.701502</v>
       </c>
       <c r="F38" t="n">
-        <v>30638.892067</v>
+        <v>30639.382986</v>
       </c>
       <c r="G38" t="n">
-        <v>42257.307359</v>
+        <v>42258.501604</v>
       </c>
       <c r="H38" t="n">
-        <v>58360.857505</v>
+        <v>58363.830727</v>
       </c>
       <c r="I38" t="n">
-        <v>82260.87134</v>
+        <v>82270.93170299999</v>
       </c>
       <c r="J38" t="n">
         <v>37297.208154</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1741.394341</v>
+        <v>1741.402351</v>
       </c>
       <c r="F39" t="n">
-        <v>2363.215664</v>
+        <v>2363.241541</v>
       </c>
       <c r="G39" t="n">
-        <v>3397.46336</v>
+        <v>3397.520909</v>
       </c>
       <c r="H39" t="n">
-        <v>4919.160453</v>
+        <v>4919.284808</v>
       </c>
       <c r="I39" t="n">
-        <v>7113.671811</v>
+        <v>7114.029209</v>
       </c>
       <c r="J39" t="n">
         <v>8017.7742</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>265.995687</v>
+        <v>265.996567</v>
       </c>
       <c r="F40" t="n">
-        <v>373.704754</v>
+        <v>373.707511</v>
       </c>
       <c r="G40" t="n">
-        <v>526.330966</v>
+        <v>526.336003</v>
       </c>
       <c r="H40" t="n">
-        <v>724.646073</v>
+        <v>724.653925</v>
       </c>
       <c r="I40" t="n">
-        <v>1009.781832</v>
+        <v>1009.796274</v>
       </c>
       <c r="J40" t="n">
         <v>1395.546389</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>313.022508</v>
+        <v>313.021045</v>
       </c>
       <c r="F41" t="n">
-        <v>485.712937</v>
+        <v>485.705547</v>
       </c>
       <c r="G41" t="n">
-        <v>706.120011</v>
+        <v>706.092326</v>
       </c>
       <c r="H41" t="n">
-        <v>992.42489</v>
+        <v>992.332009</v>
       </c>
       <c r="I41" t="n">
-        <v>1387.78527</v>
+        <v>1387.419772</v>
       </c>
       <c r="J41" t="n">
         <v>5253.075455</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1732.081432</v>
+        <v>1732.020247</v>
       </c>
       <c r="F42" t="n">
-        <v>2286.951037</v>
+        <v>2286.746854</v>
       </c>
       <c r="G42" t="n">
-        <v>3027.407703</v>
+        <v>3026.845777</v>
       </c>
       <c r="H42" t="n">
-        <v>3974.849672</v>
+        <v>3973.312265</v>
       </c>
       <c r="I42" t="n">
-        <v>5264.356386</v>
+        <v>5259.080176</v>
       </c>
       <c r="J42" t="n">
         <v>49763.582343</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>776.15454</v>
+        <v>776.159728</v>
       </c>
       <c r="F43" t="n">
-        <v>1468.379263</v>
+        <v>1468.402572</v>
       </c>
       <c r="G43" t="n">
-        <v>2644.892796</v>
+        <v>2644.963823</v>
       </c>
       <c r="H43" t="n">
-        <v>4417.788542</v>
+        <v>4417.992703</v>
       </c>
       <c r="I43" t="n">
-        <v>7263.796301</v>
+        <v>7264.563257</v>
       </c>
       <c r="J43" t="n">
         <v>5180.536209</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4446.567549</v>
+        <v>4446.587421</v>
       </c>
       <c r="F44" t="n">
-        <v>6766.240148</v>
+        <v>6766.309891</v>
       </c>
       <c r="G44" t="n">
-        <v>10636.672334</v>
+        <v>10636.833601</v>
       </c>
       <c r="H44" t="n">
-        <v>16648.958978</v>
+        <v>16649.304655</v>
       </c>
       <c r="I44" t="n">
-        <v>25767.921117</v>
+        <v>25768.863608</v>
       </c>
       <c r="J44" t="n">
         <v>33812.539997</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>534.0472580000001</v>
+        <v>534.044305</v>
       </c>
       <c r="F45" t="n">
-        <v>788.706697</v>
+        <v>788.693442</v>
       </c>
       <c r="G45" t="n">
-        <v>1139.825371</v>
+        <v>1139.776674</v>
       </c>
       <c r="H45" t="n">
-        <v>1608.122411</v>
+        <v>1607.958762</v>
       </c>
       <c r="I45" t="n">
-        <v>2266.762554</v>
+        <v>2266.11067</v>
       </c>
       <c r="J45" t="n">
         <v>9232.319035</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>14.849337</v>
+        <v>14.843701</v>
       </c>
       <c r="F46" t="n">
-        <v>23.301907</v>
+        <v>23.278092</v>
       </c>
       <c r="G46" t="n">
-        <v>37.772543</v>
+        <v>37.687663</v>
       </c>
       <c r="H46" t="n">
-        <v>60.626562</v>
+        <v>60.327969</v>
       </c>
       <c r="I46" t="n">
-        <v>97.336782</v>
+        <v>96.055723</v>
       </c>
       <c r="J46" t="n">
         <v>12802.177592</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23880.862802</v>
+        <v>23880.431582</v>
       </c>
       <c r="F47" t="n">
-        <v>39043.472381</v>
+        <v>39041.370018</v>
       </c>
       <c r="G47" t="n">
-        <v>59951.57113</v>
+        <v>59944.065924</v>
       </c>
       <c r="H47" t="n">
-        <v>89100.480066</v>
+        <v>89075.33789</v>
       </c>
       <c r="I47" t="n">
-        <v>132467.267573</v>
+        <v>132364.084064</v>
       </c>
       <c r="J47" t="n">
         <v>1191045.929977</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>285.613936</v>
+        <v>285.594588</v>
       </c>
       <c r="F48" t="n">
-        <v>404.693716</v>
+        <v>404.621047</v>
       </c>
       <c r="G48" t="n">
-        <v>574.358289</v>
+        <v>574.136307</v>
       </c>
       <c r="H48" t="n">
-        <v>797.831249</v>
+        <v>797.1716249999999</v>
       </c>
       <c r="I48" t="n">
-        <v>1108.491531</v>
+        <v>1106.061953</v>
       </c>
       <c r="J48" t="n">
         <v>22378.639226</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1052.775697</v>
+        <v>1052.778541</v>
       </c>
       <c r="F49" t="n">
-        <v>1579.975039</v>
+        <v>1579.983596</v>
       </c>
       <c r="G49" t="n">
-        <v>2288.304958</v>
+        <v>2288.317008</v>
       </c>
       <c r="H49" t="n">
-        <v>3200.271279</v>
+        <v>3200.277162</v>
       </c>
       <c r="I49" t="n">
-        <v>4444.942586</v>
+        <v>4444.90873</v>
       </c>
       <c r="J49" t="n">
         <v>6931.088838</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>28.115017</v>
+        <v>28.114838</v>
       </c>
       <c r="F50" t="n">
-        <v>38.510216</v>
+        <v>38.509503</v>
       </c>
       <c r="G50" t="n">
-        <v>49.547233</v>
+        <v>49.54509</v>
       </c>
       <c r="H50" t="n">
-        <v>61.834593</v>
+        <v>61.828677</v>
       </c>
       <c r="I50" t="n">
-        <v>77.637936</v>
+        <v>77.618177</v>
       </c>
       <c r="J50" t="n">
         <v>256.50162</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.04633</v>
+        <v>0.028814</v>
       </c>
       <c r="F51" t="n">
-        <v>0.15759</v>
+        <v>0.098012</v>
       </c>
       <c r="G51" t="n">
-        <v>0.441339</v>
+        <v>0.274494</v>
       </c>
       <c r="H51" t="n">
-        <v>1.24644</v>
+        <v>0.775257</v>
       </c>
       <c r="I51" t="n">
-        <v>4.524214</v>
+        <v>2.814246</v>
       </c>
       <c r="J51" t="n">
         <v>14785.380512</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>211.393409</v>
+        <v>211.392353</v>
       </c>
       <c r="F52" t="n">
-        <v>254.724215</v>
+        <v>254.721202</v>
       </c>
       <c r="G52" t="n">
-        <v>313.458713</v>
+        <v>313.450416</v>
       </c>
       <c r="H52" t="n">
-        <v>401.341513</v>
+        <v>401.317276</v>
       </c>
       <c r="I52" t="n">
-        <v>536.03857</v>
+        <v>535.948586</v>
       </c>
       <c r="J52" t="n">
         <v>1605.703406</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112510.407841</v>
+        <v>112510.400046</v>
       </c>
       <c r="F54" t="n">
-        <v>148196.983612</v>
+        <v>148196.95483</v>
       </c>
       <c r="G54" t="n">
-        <v>215666.097411</v>
+        <v>215666.003158</v>
       </c>
       <c r="H54" t="n">
-        <v>310244.915078</v>
+        <v>310244.612526</v>
       </c>
       <c r="I54" t="n">
-        <v>420632.79465</v>
+        <v>420631.642922</v>
       </c>
       <c r="J54" t="n">
         <v>976275.791717</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>121043.517759</v>
+        <v>121043.525554</v>
       </c>
       <c r="F55" t="n">
-        <v>148536.038748</v>
+        <v>148536.06753</v>
       </c>
       <c r="G55" t="n">
-        <v>204766.892389</v>
+        <v>204766.986642</v>
       </c>
       <c r="H55" t="n">
-        <v>283163.166622</v>
+        <v>283163.469174</v>
       </c>
       <c r="I55" t="n">
-        <v>373185.05075</v>
+        <v>373186.202478</v>
       </c>
       <c r="J55" t="n">
         <v>54746.501683</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.378694</v>
+        <v>0.170997</v>
       </c>
       <c r="F58" t="n">
-        <v>1.883046</v>
+        <v>0.85037</v>
       </c>
       <c r="G58" t="n">
-        <v>6.725982</v>
+        <v>3.037952</v>
       </c>
       <c r="H58" t="n">
-        <v>20.618829</v>
+        <v>9.316432000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>72.54684899999999</v>
+        <v>32.816497</v>
       </c>
       <c r="J58" t="n">
         <v>28210.23595</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.066638</v>
+        <v>0.03009</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3467</v>
+        <v>0.156567</v>
       </c>
       <c r="G59" t="n">
-        <v>1.293544</v>
+        <v>0.58426</v>
       </c>
       <c r="H59" t="n">
-        <v>4.002629</v>
+        <v>1.808552</v>
       </c>
       <c r="I59" t="n">
-        <v>14.069265</v>
+        <v>6.364218</v>
       </c>
       <c r="J59" t="n">
         <v>5452.333882</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.177103</v>
+        <v>0.07997</v>
       </c>
       <c r="F60" t="n">
-        <v>0.668497</v>
+        <v>0.301888</v>
       </c>
       <c r="G60" t="n">
-        <v>1.848494</v>
+        <v>0.834917</v>
       </c>
       <c r="H60" t="n">
-        <v>4.763041</v>
+        <v>2.152137</v>
       </c>
       <c r="I60" t="n">
-        <v>15.155183</v>
+        <v>6.855432</v>
       </c>
       <c r="J60" t="n">
         <v>5628.479901</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38313.564426</v>
+        <v>38315.406504</v>
       </c>
       <c r="F61" t="n">
-        <v>74847.37553600001</v>
+        <v>74856.49400799999</v>
       </c>
       <c r="G61" t="n">
-        <v>124975.110208</v>
+        <v>125005.674049</v>
       </c>
       <c r="H61" t="n">
-        <v>178070.500156</v>
+        <v>178158.651705</v>
       </c>
       <c r="I61" t="n">
-        <v>235764.081126</v>
+        <v>236060.226687</v>
       </c>
       <c r="J61" t="n">
         <v>97984.89303200001</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2871.054951</v>
+        <v>2869.009676</v>
       </c>
       <c r="F62" t="n">
-        <v>5870.190686</v>
+        <v>5858.899868</v>
       </c>
       <c r="G62" t="n">
-        <v>9983.495901</v>
+        <v>9942.976361999999</v>
       </c>
       <c r="H62" t="n">
-        <v>14117.534438</v>
+        <v>13998.686228</v>
       </c>
       <c r="I62" t="n">
-        <v>18421.019443</v>
+        <v>18029.286769</v>
       </c>
       <c r="J62" t="n">
         <v>280467.676819</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4802.69528</v>
+        <v>4801.411428</v>
       </c>
       <c r="F63" t="n">
-        <v>9685.328947</v>
+        <v>9678.51712</v>
       </c>
       <c r="G63" t="n">
-        <v>16148.259461</v>
+        <v>16124.96134</v>
       </c>
       <c r="H63" t="n">
-        <v>22930.874586</v>
+        <v>22863.258164</v>
       </c>
       <c r="I63" t="n">
-        <v>31001.516689</v>
+        <v>30767.220446</v>
       </c>
       <c r="J63" t="n">
         <v>209709.233241</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.030931</v>
+        <v>0.013967</v>
       </c>
       <c r="F64" t="n">
-        <v>0.137904</v>
+        <v>0.062276</v>
       </c>
       <c r="G64" t="n">
-        <v>0.45925</v>
+        <v>0.207431</v>
       </c>
       <c r="H64" t="n">
-        <v>1.3541</v>
+        <v>0.611838</v>
       </c>
       <c r="I64" t="n">
-        <v>4.686005</v>
+        <v>2.11971</v>
       </c>
       <c r="J64" t="n">
         <v>1800.552753</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>24279.576125</v>
+        <v>24280.089037</v>
       </c>
       <c r="F65" t="n">
-        <v>51004.275256</v>
+        <v>51006.839954</v>
       </c>
       <c r="G65" t="n">
-        <v>92286.956204</v>
+        <v>92295.523206</v>
       </c>
       <c r="H65" t="n">
-        <v>141400.35208</v>
+        <v>141425.004912</v>
       </c>
       <c r="I65" t="n">
-        <v>199808.002317</v>
+        <v>199890.105438</v>
       </c>
       <c r="J65" t="n">
         <v>214373.151316</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14342.493589</v>
+        <v>14343.203724</v>
       </c>
       <c r="F66" t="n">
-        <v>29724.180455</v>
+        <v>29727.881636</v>
       </c>
       <c r="G66" t="n">
-        <v>53241.107209</v>
+        <v>53254.277805</v>
       </c>
       <c r="H66" t="n">
-        <v>80769.414286</v>
+        <v>80809.44585800001</v>
       </c>
       <c r="I66" t="n">
-        <v>112995.063158</v>
+        <v>113135.829084</v>
       </c>
       <c r="J66" t="n">
         <v>50761.28067</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>307.993157</v>
+        <v>307.916127</v>
       </c>
       <c r="F67" t="n">
-        <v>655.63566</v>
+        <v>655.191295</v>
       </c>
       <c r="G67" t="n">
-        <v>1250.821195</v>
+        <v>1248.957483</v>
       </c>
       <c r="H67" t="n">
-        <v>2035.776319</v>
+        <v>2029.13567</v>
       </c>
       <c r="I67" t="n">
-        <v>3055.227503</v>
+        <v>3028.361793</v>
       </c>
       <c r="J67" t="n">
         <v>25993.280651</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1017.108585</v>
+        <v>1016.846032</v>
       </c>
       <c r="F68" t="n">
-        <v>2141.837289</v>
+        <v>2140.32466</v>
       </c>
       <c r="G68" t="n">
-        <v>4090.886625</v>
+        <v>4084.446669</v>
       </c>
       <c r="H68" t="n">
-        <v>6486.127238</v>
+        <v>6463.770111</v>
       </c>
       <c r="I68" t="n">
-        <v>9166.516157</v>
+        <v>9082.772733</v>
       </c>
       <c r="J68" t="n">
         <v>71668.819124</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.066512</v>
+        <v>0.030033</v>
       </c>
       <c r="F69" t="n">
-        <v>0.32673</v>
+        <v>0.147549</v>
       </c>
       <c r="G69" t="n">
-        <v>1.116592</v>
+        <v>0.504336</v>
       </c>
       <c r="H69" t="n">
-        <v>3.259652</v>
+        <v>1.472844</v>
       </c>
       <c r="I69" t="n">
-        <v>11.062934</v>
+        <v>5.004307</v>
       </c>
       <c r="J69" t="n">
         <v>4249.551341</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8214.509076</v>
+        <v>8214.982178</v>
       </c>
       <c r="F70" t="n">
-        <v>16364.8322</v>
+        <v>16367.217781</v>
       </c>
       <c r="G70" t="n">
-        <v>28726.820203</v>
+        <v>28735.194439</v>
       </c>
       <c r="H70" t="n">
-        <v>43219.774183</v>
+        <v>43245.13221</v>
       </c>
       <c r="I70" t="n">
-        <v>60466.128208</v>
+        <v>60555.590527</v>
       </c>
       <c r="J70" t="n">
         <v>16998.547408</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>24071.499991</v>
+        <v>24072.523317</v>
       </c>
       <c r="F71" t="n">
-        <v>51744.594545</v>
+        <v>51750.016797</v>
       </c>
       <c r="G71" t="n">
-        <v>89415.72689400001</v>
+        <v>89434.308919</v>
       </c>
       <c r="H71" t="n">
-        <v>127970.55844</v>
+        <v>128024.257568</v>
       </c>
       <c r="I71" t="n">
-        <v>167555.363456</v>
+        <v>167734.129338</v>
       </c>
       <c r="J71" t="n">
         <v>91003.613858</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12646.221236</v>
+        <v>12646.658666</v>
       </c>
       <c r="F72" t="n">
-        <v>23209.759928</v>
+        <v>23211.792853</v>
       </c>
       <c r="G72" t="n">
-        <v>37739.560845</v>
+        <v>37746.085906</v>
       </c>
       <c r="H72" t="n">
-        <v>53333.568918</v>
+        <v>53351.811195</v>
       </c>
       <c r="I72" t="n">
-        <v>70968.97971499999</v>
+        <v>71028.826566</v>
       </c>
       <c r="J72" t="n">
         <v>51159.434538</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>23.158696</v>
+        <v>22.236961</v>
       </c>
       <c r="F73" t="n">
-        <v>37.923327</v>
+        <v>34.684562</v>
       </c>
       <c r="G73" t="n">
-        <v>51.290963</v>
+        <v>44.20439</v>
       </c>
       <c r="H73" t="n">
-        <v>70.873053</v>
+        <v>55.707851</v>
       </c>
       <c r="I73" t="n">
-        <v>128.757818</v>
+        <v>85.548936</v>
       </c>
       <c r="J73" t="n">
         <v>27697.616854</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.02501</v>
+        <v>0.011293</v>
       </c>
       <c r="F74" t="n">
-        <v>0.150393</v>
+        <v>0.067916</v>
       </c>
       <c r="G74" t="n">
-        <v>0.546929</v>
+        <v>0.247034</v>
       </c>
       <c r="H74" t="n">
-        <v>1.58955</v>
+        <v>0.718224</v>
       </c>
       <c r="I74" t="n">
-        <v>5.263674</v>
+        <v>2.381018</v>
       </c>
       <c r="J74" t="n">
         <v>1959.728162</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7991.817606</v>
+        <v>7991.814277</v>
       </c>
       <c r="F75" t="n">
-        <v>8700.453116000001</v>
+        <v>8700.449424</v>
       </c>
       <c r="G75" t="n">
-        <v>9927.957485000001</v>
+        <v>9927.968645999999</v>
       </c>
       <c r="H75" t="n">
-        <v>12075.50643</v>
+        <v>12075.563964</v>
       </c>
       <c r="I75" t="n">
-        <v>14522.730846</v>
+        <v>14522.951788</v>
       </c>
       <c r="J75" t="n">
         <v>26796.60957</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6287.493804</v>
+        <v>6287.580954</v>
       </c>
       <c r="F76" t="n">
-        <v>7083.70122</v>
+        <v>7084.0036</v>
       </c>
       <c r="G76" t="n">
-        <v>6628.594184</v>
+        <v>6629.196683</v>
       </c>
       <c r="H76" t="n">
-        <v>6884.97773</v>
+        <v>6886.243947</v>
       </c>
       <c r="I76" t="n">
-        <v>7706.909714</v>
+        <v>7710.440348</v>
       </c>
       <c r="J76" t="n">
         <v>142165.062051</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>30570.807713</v>
+        <v>30570.773415</v>
       </c>
       <c r="F77" t="n">
-        <v>37837.823482</v>
+        <v>37837.729275</v>
       </c>
       <c r="G77" t="n">
-        <v>45304.639363</v>
+        <v>45304.473174</v>
       </c>
       <c r="H77" t="n">
-        <v>53345.742365</v>
+        <v>53345.425729</v>
       </c>
       <c r="I77" t="n">
-        <v>59032.349285</v>
+        <v>59031.536532</v>
       </c>
       <c r="J77" t="n">
         <v>38061.12503</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34436.974905</v>
+        <v>34437.057255</v>
       </c>
       <c r="F78" t="n">
-        <v>32590.325953</v>
+        <v>32590.55698</v>
       </c>
       <c r="G78" t="n">
-        <v>31585.969671</v>
+        <v>31586.487147</v>
       </c>
       <c r="H78" t="n">
-        <v>34829.787578</v>
+        <v>34831.01176</v>
       </c>
       <c r="I78" t="n">
-        <v>40494.232371</v>
+        <v>40497.905487</v>
       </c>
       <c r="J78" t="n">
         <v>190358.438197</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>40138.773022</v>
+        <v>40138.71631</v>
       </c>
       <c r="F79" t="n">
-        <v>57479.36422</v>
+        <v>57479.167171</v>
       </c>
       <c r="G79" t="n">
-        <v>86449.527394</v>
+        <v>86449.019289</v>
       </c>
       <c r="H79" t="n">
-        <v>130602.459382</v>
+        <v>130601.077785</v>
       </c>
       <c r="I79" t="n">
-        <v>182822.5687</v>
+        <v>182817.981673</v>
       </c>
       <c r="J79" t="n">
         <v>61000.204746</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>799.234999</v>
+        <v>799.2365579999999</v>
       </c>
       <c r="F80" t="n">
-        <v>749.662247</v>
+        <v>749.666548</v>
       </c>
       <c r="G80" t="n">
-        <v>751.384304</v>
+        <v>751.394595</v>
       </c>
       <c r="H80" t="n">
-        <v>881.221601</v>
+        <v>881.248657</v>
       </c>
       <c r="I80" t="n">
-        <v>1096.625418</v>
+        <v>1096.716229</v>
       </c>
       <c r="J80" t="n">
         <v>5307.226033</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>61473.735945</v>
+        <v>61473.646936</v>
       </c>
       <c r="F81" t="n">
-        <v>90524.50397799999</v>
+        <v>90524.183227</v>
       </c>
       <c r="G81" t="n">
-        <v>136965.97367</v>
+        <v>136965.127279</v>
       </c>
       <c r="H81" t="n">
-        <v>207197.580793</v>
+        <v>207195.23863</v>
       </c>
       <c r="I81" t="n">
-        <v>290674.017819</v>
+        <v>290666.141719</v>
       </c>
       <c r="J81" t="n">
         <v>71932.87081199999</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>11.415606</v>
+        <v>11.435751</v>
       </c>
       <c r="F82" t="n">
-        <v>13.797375</v>
+        <v>13.863516</v>
       </c>
       <c r="G82" t="n">
-        <v>18.080564</v>
+        <v>18.249143</v>
       </c>
       <c r="H82" t="n">
-        <v>29.236628</v>
+        <v>29.690734</v>
       </c>
       <c r="I82" t="n">
-        <v>62.765707</v>
+        <v>64.264489</v>
       </c>
       <c r="J82" t="n">
         <v>60953.331001</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24680.681399</v>
+        <v>24680.673543</v>
       </c>
       <c r="F83" t="n">
-        <v>36132.163258</v>
+        <v>36132.175107</v>
       </c>
       <c r="G83" t="n">
-        <v>53521.358265</v>
+        <v>53521.568944</v>
       </c>
       <c r="H83" t="n">
-        <v>79070.23783500001</v>
+        <v>79071.249136</v>
       </c>
       <c r="I83" t="n">
-        <v>108114.155659</v>
+        <v>108118.417255</v>
       </c>
       <c r="J83" t="n">
         <v>330664.386502</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>28444.964904</v>
+        <v>28444.981329</v>
       </c>
       <c r="F86" t="n">
-        <v>35358.178943</v>
+        <v>35358.234288</v>
       </c>
       <c r="G86" t="n">
-        <v>45749.073414</v>
+        <v>45749.226927</v>
       </c>
       <c r="H86" t="n">
-        <v>61220.455167</v>
+        <v>61220.889156</v>
       </c>
       <c r="I86" t="n">
-        <v>78795.518681</v>
+        <v>78796.97696499999</v>
       </c>
       <c r="J86" t="n">
         <v>42139.669894</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1297.159396</v>
+        <v>1297.156573</v>
       </c>
       <c r="F87" t="n">
-        <v>1814.805912</v>
+        <v>1814.794363</v>
       </c>
       <c r="G87" t="n">
-        <v>2694.825121</v>
+        <v>2694.785342</v>
       </c>
       <c r="H87" t="n">
-        <v>4045.248922</v>
+        <v>4045.116014</v>
       </c>
       <c r="I87" t="n">
-        <v>5706.833005</v>
+        <v>5706.326368</v>
       </c>
       <c r="J87" t="n">
         <v>30074.314531</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>30591.280064</v>
+        <v>30591.265734</v>
       </c>
       <c r="F88" t="n">
-        <v>34157.931425</v>
+        <v>34157.898567</v>
       </c>
       <c r="G88" t="n">
-        <v>40819.278743</v>
+        <v>40819.216679</v>
       </c>
       <c r="H88" t="n">
-        <v>52965.161469</v>
+        <v>52965.024097</v>
       </c>
       <c r="I88" t="n">
-        <v>68316.573953</v>
+        <v>68316.152315</v>
       </c>
       <c r="J88" t="n">
         <v>105818.343529</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5064.972775</v>
+        <v>5064.974211</v>
       </c>
       <c r="F89" t="n">
-        <v>5999.373948</v>
+        <v>5999.378921</v>
       </c>
       <c r="G89" t="n">
-        <v>7734.520305</v>
+        <v>7734.534239</v>
       </c>
       <c r="H89" t="n">
-        <v>10365.06529</v>
+        <v>10365.105053</v>
       </c>
       <c r="I89" t="n">
-        <v>13364.976875</v>
+        <v>13365.11168</v>
       </c>
       <c r="J89" t="n">
         <v>11562.73332</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10481.640974</v>
+        <v>10481.626016</v>
       </c>
       <c r="F90" t="n">
-        <v>12613.114386</v>
+        <v>12613.065878</v>
       </c>
       <c r="G90" t="n">
-        <v>16625.67234</v>
+        <v>16625.531047</v>
       </c>
       <c r="H90" t="n">
-        <v>22909.596077</v>
+        <v>22909.171538</v>
       </c>
       <c r="I90" t="n">
-        <v>30246.915759</v>
+        <v>30245.411119</v>
       </c>
       <c r="J90" t="n">
         <v>101338.966503</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5448.116445</v>
+        <v>5448.114146</v>
       </c>
       <c r="F91" t="n">
-        <v>6764.607252</v>
+        <v>6764.599009</v>
       </c>
       <c r="G91" t="n">
-        <v>8831.694199</v>
+        <v>8831.669980999999</v>
       </c>
       <c r="H91" t="n">
-        <v>11718.483016</v>
+        <v>11718.415168</v>
       </c>
       <c r="I91" t="n">
-        <v>14716.137159</v>
+        <v>14715.920751</v>
       </c>
       <c r="J91" t="n">
         <v>26059.672932</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>9015.395484999999</v>
+        <v>9015.400055</v>
       </c>
       <c r="F92" t="n">
-        <v>11280.392942</v>
+        <v>11280.408297</v>
       </c>
       <c r="G92" t="n">
-        <v>15192.072957</v>
+        <v>15192.115928</v>
       </c>
       <c r="H92" t="n">
-        <v>20716.240113</v>
+        <v>20716.361764</v>
       </c>
       <c r="I92" t="n">
-        <v>26643.475519</v>
+        <v>26643.882279</v>
       </c>
       <c r="J92" t="n">
         <v>17406.063426</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>331.148207</v>
+        <v>331.146794</v>
       </c>
       <c r="F93" t="n">
-        <v>434.376416</v>
+        <v>434.371159</v>
       </c>
       <c r="G93" t="n">
-        <v>620.050009</v>
+        <v>620.032797</v>
       </c>
       <c r="H93" t="n">
-        <v>921.446553</v>
+        <v>921.388791</v>
       </c>
       <c r="I93" t="n">
-        <v>1300.306857</v>
+        <v>1300.081237</v>
       </c>
       <c r="J93" t="n">
         <v>11870.530915</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>73647.05566500001</v>
+        <v>73647.011743</v>
       </c>
       <c r="F94" t="n">
-        <v>96962.37663499999</v>
+        <v>96962.20004</v>
       </c>
       <c r="G94" t="n">
-        <v>130029.871824</v>
+        <v>130029.334863</v>
       </c>
       <c r="H94" t="n">
-        <v>176662.528086</v>
+        <v>176660.962502</v>
       </c>
       <c r="I94" t="n">
-        <v>227305.899744</v>
+        <v>227300.644482</v>
       </c>
       <c r="J94" t="n">
         <v>493866.590633</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>85071.87478300001</v>
+        <v>85071.928958</v>
       </c>
       <c r="F95" t="n">
-        <v>113928.403134</v>
+        <v>113928.595584</v>
       </c>
       <c r="G95" t="n">
-        <v>158741.322573</v>
+        <v>158741.8813</v>
       </c>
       <c r="H95" t="n">
-        <v>223678.858284</v>
+        <v>223680.482955</v>
       </c>
       <c r="I95" t="n">
-        <v>297499.759938</v>
+        <v>297505.301144</v>
       </c>
       <c r="J95" t="n">
         <v>162839.237099</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>19610.579093</v>
+        <v>19610.577669</v>
       </c>
       <c r="F96" t="n">
-        <v>22905.839991</v>
+        <v>22905.838611</v>
       </c>
       <c r="G96" t="n">
-        <v>27569.904938</v>
+        <v>27569.911265</v>
       </c>
       <c r="H96" t="n">
-        <v>35458.116591</v>
+        <v>35458.15046</v>
       </c>
       <c r="I96" t="n">
-        <v>45004.847396</v>
+        <v>45004.98436</v>
       </c>
       <c r="J96" t="n">
         <v>51732.017522</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>14139.712209</v>
+        <v>14139.716772</v>
       </c>
       <c r="F97" t="n">
-        <v>15255.990316</v>
+        <v>15256.006583</v>
       </c>
       <c r="G97" t="n">
-        <v>17819.645877</v>
+        <v>17819.691932</v>
       </c>
       <c r="H97" t="n">
-        <v>22828.242832</v>
+        <v>22828.374902</v>
       </c>
       <c r="I97" t="n">
-        <v>29303.130714</v>
+        <v>29303.582901</v>
       </c>
       <c r="J97" t="n">
         <v>19540.843296</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>157678.759456</v>
+        <v>157678.933127</v>
       </c>
       <c r="F98" t="n">
-        <v>168785.490517</v>
+        <v>168786.010426</v>
       </c>
       <c r="G98" t="n">
-        <v>194307.66241</v>
+        <v>194309.029197</v>
       </c>
       <c r="H98" t="n">
-        <v>225855.197379</v>
+        <v>225858.764946</v>
       </c>
       <c r="I98" t="n">
-        <v>257360.767929</v>
+        <v>257371.93561</v>
       </c>
       <c r="J98" t="n">
         <v>105718.596123</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>47897.337329</v>
+        <v>47897.243032</v>
       </c>
       <c r="F99" t="n">
-        <v>59241.804504</v>
+        <v>59241.479674</v>
       </c>
       <c r="G99" t="n">
-        <v>79884.554603</v>
+        <v>79883.579056</v>
       </c>
       <c r="H99" t="n">
-        <v>104938.130659</v>
+        <v>104935.346747</v>
       </c>
       <c r="I99" t="n">
-        <v>130246.906797</v>
+        <v>130237.73276</v>
       </c>
       <c r="J99" t="n">
         <v>319350.188372</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>62754.240228</v>
+        <v>62754.287484</v>
       </c>
       <c r="F100" t="n">
-        <v>66726.537197</v>
+        <v>66726.685404</v>
       </c>
       <c r="G100" t="n">
-        <v>78102.698347</v>
+        <v>78103.10958600001</v>
       </c>
       <c r="H100" t="n">
-        <v>92645.538573</v>
+        <v>92646.66177799999</v>
       </c>
       <c r="I100" t="n">
-        <v>107644.796073</v>
+        <v>107648.439838</v>
       </c>
       <c r="J100" t="n">
         <v>62169.683511</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>101161.207477</v>
+        <v>101161.334352</v>
       </c>
       <c r="F101" t="n">
-        <v>115274.824825</v>
+        <v>115275.217204</v>
       </c>
       <c r="G101" t="n">
-        <v>143024.618116</v>
+        <v>143025.694751</v>
       </c>
       <c r="H101" t="n">
-        <v>176162.348807</v>
+        <v>176165.262829</v>
       </c>
       <c r="I101" t="n">
-        <v>208745.63791</v>
+        <v>208755.00236</v>
       </c>
       <c r="J101" t="n">
         <v>83573.473469</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>305747.606994</v>
+        <v>305747.325265</v>
       </c>
       <c r="F102" t="n">
-        <v>368931.768811</v>
+        <v>368930.848894</v>
       </c>
       <c r="G102" t="n">
-        <v>490255.00251</v>
+        <v>490252.33112</v>
       </c>
       <c r="H102" t="n">
-        <v>643031.310758</v>
+        <v>643023.759575</v>
       </c>
       <c r="I102" t="n">
-        <v>804148.418216</v>
+        <v>804123.341039</v>
       </c>
       <c r="J102" t="n">
         <v>1438214.464511</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>625606.60905</v>
+        <v>625606.778832</v>
       </c>
       <c r="F103" t="n">
-        <v>644988.760361</v>
+        <v>644989.421582</v>
       </c>
       <c r="G103" t="n">
-        <v>722211.561855</v>
+        <v>722213.671476</v>
       </c>
       <c r="H103" t="n">
-        <v>823212.527336</v>
+        <v>823218.662486</v>
       </c>
       <c r="I103" t="n">
-        <v>926494.924975</v>
+        <v>926515.297362</v>
       </c>
       <c r="J103" t="n">
         <v>700076.370566</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>49210.722458</v>
+        <v>49210.685172</v>
       </c>
       <c r="F104" t="n">
-        <v>57271.268736</v>
+        <v>57271.152369</v>
       </c>
       <c r="G104" t="n">
-        <v>73062.197011</v>
+        <v>73061.879019</v>
       </c>
       <c r="H104" t="n">
-        <v>93594.322268</v>
+        <v>93593.43619399999</v>
       </c>
       <c r="I104" t="n">
-        <v>115391.963689</v>
+        <v>115388.997407</v>
       </c>
       <c r="J104" t="n">
         <v>194683.918597</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26406.86886</v>
+        <v>26406.849486</v>
       </c>
       <c r="F105" t="n">
-        <v>31001.464881</v>
+        <v>31001.40986</v>
       </c>
       <c r="G105" t="n">
-        <v>40337.786682</v>
+        <v>40337.644058</v>
       </c>
       <c r="H105" t="n">
-        <v>51868.722759</v>
+        <v>51868.361609</v>
       </c>
       <c r="I105" t="n">
-        <v>63697.561982</v>
+        <v>63696.487798</v>
       </c>
       <c r="J105" t="n">
         <v>94238.57118499999</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>360892.673312</v>
+        <v>360892.680673</v>
       </c>
       <c r="F106" t="n">
-        <v>439268.074217</v>
+        <v>439268.044032</v>
       </c>
       <c r="G106" t="n">
-        <v>593821.286938</v>
+        <v>593821.012359</v>
       </c>
       <c r="H106" t="n">
-        <v>783431.400344</v>
+        <v>783430.281712</v>
       </c>
       <c r="I106" t="n">
-        <v>975044.330516</v>
+        <v>975040.0319919999</v>
       </c>
       <c r="J106" t="n">
         <v>1267110.899402</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1427.709994</v>
+        <v>1427.670892</v>
       </c>
       <c r="F107" t="n">
-        <v>1832.210877</v>
+        <v>1832.074527</v>
       </c>
       <c r="G107" t="n">
-        <v>2430.782237</v>
+        <v>2430.398305</v>
       </c>
       <c r="H107" t="n">
-        <v>3160.03072</v>
+        <v>3158.983636</v>
       </c>
       <c r="I107" t="n">
-        <v>3954.297232</v>
+        <v>3950.882383</v>
       </c>
       <c r="J107" t="n">
         <v>65931.499134</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>45360.961253</v>
+        <v>45360.686911</v>
       </c>
       <c r="F108" t="n">
-        <v>52605.735703</v>
+        <v>52604.899182</v>
       </c>
       <c r="G108" t="n">
-        <v>65550.362936</v>
+        <v>65548.184957</v>
       </c>
       <c r="H108" t="n">
-        <v>80985.21851999999</v>
+        <v>80979.627859</v>
       </c>
       <c r="I108" t="n">
-        <v>96302.084852</v>
+        <v>96284.890979</v>
       </c>
       <c r="J108" t="n">
         <v>404214.496445</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>80763.238186</v>
+        <v>80763.327582</v>
       </c>
       <c r="F109" t="n">
-        <v>94196.163529</v>
+        <v>94196.443337</v>
       </c>
       <c r="G109" t="n">
-        <v>125807.958538</v>
+        <v>125808.758665</v>
       </c>
       <c r="H109" t="n">
-        <v>170416.549465</v>
+        <v>170418.833812</v>
       </c>
       <c r="I109" t="n">
-        <v>222580.225486</v>
+        <v>222587.970452</v>
       </c>
       <c r="J109" t="n">
         <v>144166.079984</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>339653.668472</v>
+        <v>339654.191709</v>
       </c>
       <c r="F110" t="n">
-        <v>417500.513628</v>
+        <v>417502.22929</v>
       </c>
       <c r="G110" t="n">
-        <v>563121.337029</v>
+        <v>563126.3530839999</v>
       </c>
       <c r="H110" t="n">
-        <v>740486.705599</v>
+        <v>740500.970475</v>
       </c>
       <c r="I110" t="n">
-        <v>919121.618558</v>
+        <v>919169.116047</v>
       </c>
       <c r="J110" t="n">
         <v>273242.366236</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>321735.664631</v>
+        <v>321735.737424</v>
       </c>
       <c r="F111" t="n">
-        <v>385521.987288</v>
+        <v>385522.211118</v>
       </c>
       <c r="G111" t="n">
-        <v>500973.234023</v>
+        <v>500973.88257</v>
       </c>
       <c r="H111" t="n">
-        <v>640969.41902</v>
+        <v>640971.316678</v>
       </c>
       <c r="I111" t="n">
-        <v>786157.741264</v>
+        <v>786164.294903</v>
       </c>
       <c r="J111" t="n">
         <v>834689.110708</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>276267.4323</v>
+        <v>276266.96806</v>
       </c>
       <c r="F112" t="n">
-        <v>334880.821926</v>
+        <v>334879.300101</v>
       </c>
       <c r="G112" t="n">
-        <v>448809.432767</v>
+        <v>448804.947798</v>
       </c>
       <c r="H112" t="n">
-        <v>592232.507794</v>
+        <v>592219.659664</v>
       </c>
       <c r="I112" t="n">
-        <v>743574.694524</v>
+        <v>743531.549071</v>
       </c>
       <c r="J112" t="n">
         <v>1695079.451758</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>980.345061</v>
+        <v>980.311461</v>
       </c>
       <c r="F113" t="n">
-        <v>1394.919915</v>
+        <v>1394.775131</v>
       </c>
       <c r="G113" t="n">
-        <v>1792.143749</v>
+        <v>1791.736981</v>
       </c>
       <c r="H113" t="n">
-        <v>2527.505816</v>
+        <v>2526.305029</v>
       </c>
       <c r="I113" t="n">
-        <v>3469.09462</v>
+        <v>3464.839616</v>
       </c>
       <c r="J113" t="n">
         <v>42258.316291</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1011.970575</v>
+        <v>1011.97288</v>
       </c>
       <c r="F114" t="n">
-        <v>2040.070227</v>
+        <v>2040.082796</v>
       </c>
       <c r="G114" t="n">
-        <v>3929.175905</v>
+        <v>3929.221048</v>
       </c>
       <c r="H114" t="n">
-        <v>7285.635607</v>
+        <v>7285.784332</v>
       </c>
       <c r="I114" t="n">
-        <v>11502.235708</v>
+        <v>11502.763678</v>
       </c>
       <c r="J114" t="n">
         <v>11484.760525</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>25045.468364</v>
+        <v>25045.499659</v>
       </c>
       <c r="F115" t="n">
-        <v>40962.316578</v>
+        <v>40962.448793</v>
       </c>
       <c r="G115" t="n">
-        <v>65870.797896</v>
+        <v>65871.15952099999</v>
       </c>
       <c r="H115" t="n">
-        <v>109922.515537</v>
+        <v>109923.567599</v>
       </c>
       <c r="I115" t="n">
-        <v>166920.801032</v>
+        <v>166924.528066</v>
       </c>
       <c r="J115" t="n">
         <v>199533.477444</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>20985.048426</v>
+        <v>20984.964911</v>
       </c>
       <c r="F116" t="n">
-        <v>22103.680061</v>
+        <v>22103.453641</v>
       </c>
       <c r="G116" t="n">
-        <v>24764.462226</v>
+        <v>24763.938373</v>
       </c>
       <c r="H116" t="n">
-        <v>29626.96418</v>
+        <v>29625.674617</v>
       </c>
       <c r="I116" t="n">
-        <v>35336.4844</v>
+        <v>35332.544152</v>
       </c>
       <c r="J116" t="n">
         <v>7940.547627</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>19761.047335</v>
+        <v>19761.018893</v>
       </c>
       <c r="F117" t="n">
-        <v>25145.291161</v>
+        <v>25145.209001</v>
       </c>
       <c r="G117" t="n">
-        <v>30251.946583</v>
+        <v>30251.753692</v>
       </c>
       <c r="H117" t="n">
-        <v>37131.445765</v>
+        <v>37130.970517</v>
       </c>
       <c r="I117" t="n">
-        <v>44353.648519</v>
+        <v>44352.205649</v>
       </c>
       <c r="J117" t="n">
         <v>40787.344567</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>26735.676611</v>
+        <v>26735.705759</v>
       </c>
       <c r="F118" t="n">
-        <v>26962.970685</v>
+        <v>26963.044401</v>
       </c>
       <c r="G118" t="n">
-        <v>28621.175584</v>
+        <v>28621.328236</v>
       </c>
       <c r="H118" t="n">
-        <v>32657.346817</v>
+        <v>32657.684676</v>
       </c>
       <c r="I118" t="n">
-        <v>37505.398608</v>
+        <v>37506.34015</v>
       </c>
       <c r="J118" t="n">
         <v>52165.125992</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>7223.1749</v>
+        <v>7223.175241</v>
       </c>
       <c r="F119" t="n">
-        <v>8793.184669</v>
+        <v>8793.189462</v>
       </c>
       <c r="G119" t="n">
-        <v>11114.892792</v>
+        <v>11114.912694</v>
       </c>
       <c r="H119" t="n">
-        <v>14544.592203</v>
+        <v>14544.658934</v>
       </c>
       <c r="I119" t="n">
-        <v>18441.117146</v>
+        <v>18441.356749</v>
       </c>
       <c r="J119" t="n">
         <v>25765.715088</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5307.763574</v>
+        <v>5307.750778</v>
       </c>
       <c r="F120" t="n">
-        <v>5628.3193</v>
+        <v>5628.284412</v>
       </c>
       <c r="G120" t="n">
-        <v>6356.940076</v>
+        <v>6356.858641</v>
       </c>
       <c r="H120" t="n">
-        <v>7680.170247</v>
+        <v>7679.96756</v>
       </c>
       <c r="I120" t="n">
-        <v>9272.909153000001</v>
+        <v>9272.281647</v>
       </c>
       <c r="J120" t="n">
         <v>5795.0235</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>36005.651984</v>
+        <v>36005.665357</v>
       </c>
       <c r="F121" t="n">
-        <v>43291.8194</v>
+        <v>43291.881518</v>
       </c>
       <c r="G121" t="n">
-        <v>53887.122025</v>
+        <v>53887.320688</v>
       </c>
       <c r="H121" t="n">
-        <v>68712.65427899999</v>
+        <v>68713.23085199999</v>
       </c>
       <c r="I121" t="n">
-        <v>84331.634158</v>
+        <v>84333.50098700001</v>
       </c>
       <c r="J121" t="n">
         <v>120260.324046</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>297820.568171</v>
+        <v>297820.650061</v>
       </c>
       <c r="F122" t="n">
-        <v>317593.980264</v>
+        <v>317594.183105</v>
       </c>
       <c r="G122" t="n">
-        <v>362559.270704</v>
+        <v>362559.697666</v>
       </c>
       <c r="H122" t="n">
-        <v>444928.466199</v>
+        <v>444929.452534</v>
       </c>
       <c r="I122" t="n">
-        <v>547825.832805</v>
+        <v>547828.795457</v>
       </c>
       <c r="J122" t="n">
         <v>719719.837971</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>66902.538636</v>
+        <v>66934.329874</v>
       </c>
       <c r="F123" t="n">
-        <v>72169.411196</v>
+        <v>72248.681415</v>
       </c>
       <c r="G123" t="n">
-        <v>81471.034747</v>
+        <v>81634.936686</v>
       </c>
       <c r="H123" t="n">
-        <v>90797.353428</v>
+        <v>91130.742191</v>
       </c>
       <c r="I123" t="n">
-        <v>97903.291799</v>
+        <v>98688.285909</v>
       </c>
       <c r="J123" t="n">
         <v>31960.603352</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>499732.457125</v>
+        <v>499862.047517</v>
       </c>
       <c r="F124" t="n">
-        <v>539915.0187219999</v>
+        <v>540233.697026</v>
       </c>
       <c r="G124" t="n">
-        <v>600939.167568</v>
+        <v>601572.743462</v>
       </c>
       <c r="H124" t="n">
-        <v>664615.7604800001</v>
+        <v>665859.023528</v>
       </c>
       <c r="I124" t="n">
-        <v>719666.614751</v>
+        <v>722477.783968</v>
       </c>
       <c r="J124" t="n">
         <v>522747.081785</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>148788.784239</v>
+        <v>148627.402609</v>
       </c>
       <c r="F125" t="n">
-        <v>151897.400802</v>
+        <v>151499.452279</v>
       </c>
       <c r="G125" t="n">
-        <v>159909.905735</v>
+        <v>159112.427902</v>
       </c>
       <c r="H125" t="n">
-        <v>175457.999692</v>
+        <v>173881.34788</v>
       </c>
       <c r="I125" t="n">
-        <v>210203.419249</v>
+        <v>206607.255923</v>
       </c>
       <c r="J125" t="n">
         <v>572890.105763</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1090.695094</v>
+        <v>1090.672242</v>
       </c>
       <c r="F130" t="n">
-        <v>7674.626932</v>
+        <v>7674.133904</v>
       </c>
       <c r="G130" t="n">
-        <v>16049.312733</v>
+        <v>16046.678457</v>
       </c>
       <c r="H130" t="n">
-        <v>26416.095382</v>
+        <v>26404.384521</v>
       </c>
       <c r="I130" t="n">
-        <v>38859.193574</v>
+        <v>38794.601759</v>
       </c>
       <c r="J130" t="n">
         <v>1880077.949883</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.001012</v>
+        <v>0.000191</v>
       </c>
       <c r="F131" t="n">
-        <v>0.027968</v>
+        <v>0.005263</v>
       </c>
       <c r="G131" t="n">
-        <v>0.147353</v>
+        <v>0.027731</v>
       </c>
       <c r="H131" t="n">
-        <v>0.609247</v>
+        <v>0.114656</v>
       </c>
       <c r="I131" t="n">
-        <v>3.142751</v>
+        <v>0.591466</v>
       </c>
       <c r="J131" t="n">
         <v>69675.986965</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>51229.126159</v>
+        <v>51229.155874</v>
       </c>
       <c r="F132" t="n">
-        <v>328721.211793</v>
+        <v>328721.746</v>
       </c>
       <c r="G132" t="n">
-        <v>608225.4013800001</v>
+        <v>608227.814733</v>
       </c>
       <c r="H132" t="n">
-        <v>884385.689089</v>
+        <v>884395.326904</v>
       </c>
       <c r="I132" t="n">
-        <v>1182386.385087</v>
+        <v>1182436.618389</v>
       </c>
       <c r="J132" t="n">
         <v>186413.361169</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>9308.209424000001</v>
+        <v>9308.21523</v>
       </c>
       <c r="F133" t="n">
-        <v>89172.70948999999</v>
+        <v>89172.857112</v>
       </c>
       <c r="G133" t="n">
-        <v>237142.438323</v>
+        <v>237143.318545</v>
       </c>
       <c r="H133" t="n">
-        <v>444238.608702</v>
+        <v>444242.857378</v>
       </c>
       <c r="I133" t="n">
-        <v>685322.024707</v>
+        <v>685347.055837</v>
       </c>
       <c r="J133" t="n">
         <v>230808.919588</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4342.410173</v>
+        <v>4342.410016</v>
       </c>
       <c r="F134" t="n">
-        <v>25909.541209</v>
+        <v>25909.545035</v>
       </c>
       <c r="G134" t="n">
-        <v>46221.244117</v>
+        <v>46221.291562</v>
       </c>
       <c r="H134" t="n">
-        <v>67334.927022</v>
+        <v>67335.220147</v>
       </c>
       <c r="I134" t="n">
-        <v>91447.39481</v>
+        <v>91449.314503</v>
       </c>
       <c r="J134" t="n">
         <v>63340.764206</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>643.671848</v>
+        <v>643.6722109999999</v>
       </c>
       <c r="F135" t="n">
-        <v>5224.45123</v>
+        <v>5224.458994</v>
       </c>
       <c r="G135" t="n">
-        <v>12349.205902</v>
+        <v>12349.24731</v>
       </c>
       <c r="H135" t="n">
-        <v>21831.131073</v>
+        <v>21831.321994</v>
       </c>
       <c r="I135" t="n">
-        <v>33417.09064</v>
+        <v>33418.20702</v>
       </c>
       <c r="J135" t="n">
         <v>14930.798422</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>107.284767</v>
+        <v>107.279855</v>
       </c>
       <c r="F136" t="n">
-        <v>648.045662</v>
+        <v>647.972621</v>
       </c>
       <c r="G136" t="n">
-        <v>1091.03451</v>
+        <v>1090.808081</v>
       </c>
       <c r="H136" t="n">
-        <v>1446.185864</v>
+        <v>1445.607461</v>
       </c>
       <c r="I136" t="n">
-        <v>1854.033014</v>
+        <v>1851.812372</v>
       </c>
       <c r="J136" t="n">
         <v>54390.922013</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1795.129672</v>
+        <v>1795.130353</v>
       </c>
       <c r="F137" t="n">
-        <v>11878.464709</v>
+        <v>11878.476169</v>
       </c>
       <c r="G137" t="n">
-        <v>21764.421241</v>
+        <v>21764.474038</v>
       </c>
       <c r="H137" t="n">
-        <v>31516.823412</v>
+        <v>31517.047606</v>
       </c>
       <c r="I137" t="n">
-        <v>41951.799955</v>
+        <v>41953.020305</v>
       </c>
       <c r="J137" t="n">
         <v>21028.591279</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>14.30488</v>
+        <v>14.304027</v>
       </c>
       <c r="F138" t="n">
-        <v>93.248694</v>
+        <v>93.232692</v>
       </c>
       <c r="G138" t="n">
-        <v>176.795012</v>
+        <v>176.726376</v>
       </c>
       <c r="H138" t="n">
-        <v>261.208113</v>
+        <v>260.971662</v>
       </c>
       <c r="I138" t="n">
-        <v>347.25063</v>
+        <v>346.228994</v>
       </c>
       <c r="J138" t="n">
         <v>24097.096424</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.000167</v>
+        <v>3.1e-05</v>
       </c>
       <c r="F139" t="n">
-        <v>0.00353</v>
+        <v>0.000664</v>
       </c>
       <c r="G139" t="n">
-        <v>0.018619</v>
+        <v>0.003504</v>
       </c>
       <c r="H139" t="n">
-        <v>0.082248</v>
+        <v>0.015478</v>
       </c>
       <c r="I139" t="n">
-        <v>0.452398</v>
+        <v>0.08514099999999999</v>
       </c>
       <c r="J139" t="n">
         <v>10348.574923</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>164.503763</v>
+        <v>164.495862</v>
       </c>
       <c r="F140" t="n">
-        <v>990.236394</v>
+        <v>990.1184940000001</v>
       </c>
       <c r="G140" t="n">
-        <v>1795.871065</v>
+        <v>1795.42605</v>
       </c>
       <c r="H140" t="n">
-        <v>2683.843003</v>
+        <v>2682.289604</v>
       </c>
       <c r="I140" t="n">
-        <v>3762.148497</v>
+        <v>3754.601928</v>
       </c>
       <c r="J140" t="n">
         <v>209339.642728</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1476.869254</v>
+        <v>1476.87012</v>
       </c>
       <c r="F141" t="n">
-        <v>10479.126497</v>
+        <v>10479.143429</v>
       </c>
       <c r="G141" t="n">
-        <v>21822.354482</v>
+        <v>21822.438682</v>
       </c>
       <c r="H141" t="n">
-        <v>35289.264982</v>
+        <v>35289.633057</v>
       </c>
       <c r="I141" t="n">
-        <v>51068.448985</v>
+        <v>51070.50926</v>
       </c>
       <c r="J141" t="n">
         <v>11835.522475</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>414.810786</v>
+        <v>414.810988</v>
       </c>
       <c r="F142" t="n">
-        <v>4533.047782</v>
+        <v>4533.051512</v>
       </c>
       <c r="G142" t="n">
-        <v>15049.531663</v>
+        <v>15049.521333</v>
       </c>
       <c r="H142" t="n">
-        <v>33834.313763</v>
+        <v>33833.991431</v>
       </c>
       <c r="I142" t="n">
-        <v>59241.176852</v>
+        <v>59237.894926</v>
       </c>
       <c r="J142" t="n">
         <v>204795.141826</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102.600082</v>
+        <v>102.581915</v>
       </c>
       <c r="F146" t="n">
-        <v>101.095655</v>
+        <v>101.05038</v>
       </c>
       <c r="G146" t="n">
-        <v>103.716055</v>
+        <v>103.622163</v>
       </c>
       <c r="H146" t="n">
-        <v>115.748782</v>
+        <v>115.536959</v>
       </c>
       <c r="I146" t="n">
-        <v>140.94262</v>
+        <v>140.304084</v>
       </c>
       <c r="J146" t="n">
         <v>3785.040034</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1759.132067</v>
+        <v>1759.09675</v>
       </c>
       <c r="F147" t="n">
-        <v>1989.005533</v>
+        <v>1988.901721</v>
       </c>
       <c r="G147" t="n">
-        <v>2239.11368</v>
+        <v>2238.873312</v>
       </c>
       <c r="H147" t="n">
-        <v>2567.722613</v>
+        <v>2567.160633</v>
       </c>
       <c r="I147" t="n">
-        <v>3038.746371</v>
+        <v>3037.063306</v>
       </c>
       <c r="J147" t="n">
         <v>13012.310881</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>273606.901651</v>
+        <v>273606.955135</v>
       </c>
       <c r="F148" t="n">
-        <v>326250.903687</v>
+        <v>326251.052775</v>
       </c>
       <c r="G148" t="n">
-        <v>398095.29685</v>
+        <v>398095.63111</v>
       </c>
       <c r="H148" t="n">
-        <v>486737.86849</v>
+        <v>486738.642293</v>
       </c>
       <c r="I148" t="n">
-        <v>594137.495993</v>
+        <v>594139.817596</v>
       </c>
       <c r="J148" t="n">
         <v>725998.937071</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>9146.068265</v>
+        <v>9146.021766</v>
       </c>
       <c r="F149" t="n">
-        <v>10699.509824</v>
+        <v>10699.373761</v>
       </c>
       <c r="G149" t="n">
-        <v>13559.352842</v>
+        <v>13559.003047</v>
       </c>
       <c r="H149" t="n">
-        <v>17482.473974</v>
+        <v>17481.54777</v>
       </c>
       <c r="I149" t="n">
-        <v>22003.289368</v>
+        <v>22000.287495</v>
       </c>
       <c r="J149" t="n">
         <v>81842.871742</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>111879.456277</v>
+        <v>111879.306095</v>
       </c>
       <c r="F150" t="n">
-        <v>128290.437802</v>
+        <v>128290.020079</v>
       </c>
       <c r="G150" t="n">
-        <v>160780.364183</v>
+        <v>160779.28766</v>
       </c>
       <c r="H150" t="n">
-        <v>201004.093418</v>
+        <v>201001.245963</v>
       </c>
       <c r="I150" t="n">
-        <v>239971.885428</v>
+        <v>239962.837796</v>
       </c>
       <c r="J150" t="n">
         <v>440178.028068</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>46420.317673</v>
+        <v>46420.252144</v>
       </c>
       <c r="F151" t="n">
-        <v>57410.136032</v>
+        <v>57409.933468</v>
       </c>
       <c r="G151" t="n">
-        <v>76732.842107</v>
+        <v>76732.273615</v>
       </c>
       <c r="H151" t="n">
-        <v>100422.269264</v>
+        <v>100420.681359</v>
       </c>
       <c r="I151" t="n">
-        <v>123701.286239</v>
+        <v>123696.077734</v>
       </c>
       <c r="J151" t="n">
         <v>242376.588692</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>86788.97121600001</v>
+        <v>86788.703433</v>
       </c>
       <c r="F152" t="n">
-        <v>109050.357861</v>
+        <v>109049.496542</v>
       </c>
       <c r="G152" t="n">
-        <v>138822.423277</v>
+        <v>138820.172774</v>
       </c>
       <c r="H152" t="n">
-        <v>171399.456324</v>
+        <v>171393.735439</v>
       </c>
       <c r="I152" t="n">
-        <v>200791.862466</v>
+        <v>200774.639038</v>
       </c>
       <c r="J152" t="n">
         <v>519715.323887</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>189686.695578</v>
+        <v>189687.191998</v>
       </c>
       <c r="F153" t="n">
-        <v>222767.299397</v>
+        <v>222768.809423</v>
       </c>
       <c r="G153" t="n">
-        <v>291074.165666</v>
+        <v>291078.145376</v>
       </c>
       <c r="H153" t="n">
-        <v>385224.845557</v>
+        <v>385235.318859</v>
       </c>
       <c r="I153" t="n">
-        <v>490463.928212</v>
+        <v>490496.806078</v>
       </c>
       <c r="J153" t="n">
         <v>55075.099464</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>43523.050991</v>
+        <v>43523.084563</v>
       </c>
       <c r="F154" t="n">
-        <v>53355.229245</v>
+        <v>53355.336887</v>
       </c>
       <c r="G154" t="n">
-        <v>67241.57404599999</v>
+        <v>67241.83964799999</v>
       </c>
       <c r="H154" t="n">
-        <v>81664.642484</v>
+        <v>81665.25163</v>
       </c>
       <c r="I154" t="n">
-        <v>93202.903507</v>
+        <v>93204.507079</v>
       </c>
       <c r="J154" t="n">
         <v>82425.13136699999</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>50382.466789</v>
+        <v>50383.615684</v>
       </c>
       <c r="F155" t="n">
-        <v>85410.88479500001</v>
+        <v>85415.81741</v>
       </c>
       <c r="G155" t="n">
-        <v>179269.856021</v>
+        <v>179290.589834</v>
       </c>
       <c r="H155" t="n">
-        <v>312384.484249</v>
+        <v>312456.70752</v>
       </c>
       <c r="I155" t="n">
-        <v>471997.862758</v>
+        <v>472270.454889</v>
       </c>
       <c r="J155" t="n">
         <v>85732.90502400001</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3643.205344</v>
+        <v>3641.991646</v>
       </c>
       <c r="F156" t="n">
-        <v>5887.154617</v>
+        <v>5881.963701</v>
       </c>
       <c r="G156" t="n">
-        <v>11731.091819</v>
+        <v>11709.465137</v>
       </c>
       <c r="H156" t="n">
-        <v>19262.173046</v>
+        <v>19188.108757</v>
       </c>
       <c r="I156" t="n">
-        <v>27605.422236</v>
+        <v>27331.055949</v>
       </c>
       <c r="J156" t="n">
         <v>667078.1899530001</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1122.783133</v>
+        <v>1122.765383</v>
       </c>
       <c r="F157" t="n">
-        <v>2286.943679</v>
+        <v>2286.81926</v>
       </c>
       <c r="G157" t="n">
-        <v>5540.847326</v>
+        <v>5540.083634</v>
       </c>
       <c r="H157" t="n">
-        <v>10159.211181</v>
+        <v>10155.958856</v>
       </c>
       <c r="I157" t="n">
-        <v>14854.024347</v>
+        <v>14841.101825</v>
       </c>
       <c r="J157" t="n">
         <v>50467.74715</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>26735.250563</v>
+        <v>26735.174786</v>
       </c>
       <c r="F158" t="n">
-        <v>37991.00288</v>
+        <v>37990.746458</v>
       </c>
       <c r="G158" t="n">
-        <v>66225.953528</v>
+        <v>66225.131276</v>
       </c>
       <c r="H158" t="n">
-        <v>98476.63305</v>
+        <v>98473.943339</v>
       </c>
       <c r="I158" t="n">
-        <v>130975.445315</v>
+        <v>130964.130411</v>
       </c>
       <c r="J158" t="n">
         <v>210847.515655</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>477.409581</v>
+        <v>477.406534</v>
       </c>
       <c r="F159" t="n">
-        <v>737.0142949999999</v>
+        <v>737.001477</v>
       </c>
       <c r="G159" t="n">
-        <v>1422.417453</v>
+        <v>1422.362626</v>
       </c>
       <c r="H159" t="n">
-        <v>2259.840816</v>
+        <v>2259.646895</v>
       </c>
       <c r="I159" t="n">
-        <v>3116.189042</v>
+        <v>3115.436107</v>
       </c>
       <c r="J159" t="n">
         <v>6104.206251</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14446.539591</v>
+        <v>14446.700966</v>
       </c>
       <c r="F160" t="n">
-        <v>24456.298094</v>
+        <v>24456.950055</v>
       </c>
       <c r="G160" t="n">
-        <v>50329.203282</v>
+        <v>50331.736924</v>
       </c>
       <c r="H160" t="n">
-        <v>84536.941389</v>
+        <v>84544.918364</v>
       </c>
       <c r="I160" t="n">
-        <v>123318.478032</v>
+        <v>123345.242549</v>
       </c>
       <c r="J160" t="n">
         <v>129492.569697</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6.979796</v>
+        <v>6.95616</v>
       </c>
       <c r="F162" t="n">
-        <v>5.392304</v>
+        <v>5.354284</v>
       </c>
       <c r="G162" t="n">
-        <v>5.492618</v>
+        <v>5.427234</v>
       </c>
       <c r="H162" t="n">
-        <v>6.88986</v>
+        <v>6.747763</v>
       </c>
       <c r="I162" t="n">
-        <v>10.169795</v>
+        <v>9.744241000000001</v>
       </c>
       <c r="J162" t="n">
         <v>6371.518444</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1029.621231</v>
+        <v>1029.622617</v>
       </c>
       <c r="F163" t="n">
-        <v>1267.530429</v>
+        <v>1267.533327</v>
       </c>
       <c r="G163" t="n">
-        <v>2009.09258</v>
+        <v>2009.09729</v>
       </c>
       <c r="H163" t="n">
-        <v>3215.990467</v>
+        <v>3215.996049</v>
       </c>
       <c r="I163" t="n">
-        <v>4653.78683</v>
+        <v>4653.788898</v>
       </c>
       <c r="J163" t="n">
         <v>6664.200034</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>7129.236221</v>
+        <v>7129.248423</v>
       </c>
       <c r="F164" t="n">
-        <v>9624.856164999999</v>
+        <v>9624.886315</v>
       </c>
       <c r="G164" t="n">
-        <v>16214.730203</v>
+        <v>16214.795461</v>
       </c>
       <c r="H164" t="n">
-        <v>27673.779068</v>
+        <v>27673.909732</v>
       </c>
       <c r="I164" t="n">
-        <v>42810.551625</v>
+        <v>42810.813166</v>
       </c>
       <c r="J164" t="n">
         <v>62921.855626</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>47887.641394</v>
+        <v>47887.793269</v>
       </c>
       <c r="F165" t="n">
-        <v>56592.998625</v>
+        <v>56593.428691</v>
       </c>
       <c r="G165" t="n">
-        <v>74965.389564</v>
+        <v>74966.513593</v>
       </c>
       <c r="H165" t="n">
-        <v>105612.362796</v>
+        <v>105615.592867</v>
       </c>
       <c r="I165" t="n">
-        <v>142933.441001</v>
+        <v>142944.846021</v>
       </c>
       <c r="J165" t="n">
         <v>13917.660088</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>32772.685499</v>
+        <v>32772.776763</v>
       </c>
       <c r="F166" t="n">
-        <v>36636.132605</v>
+        <v>36636.372034</v>
       </c>
       <c r="G166" t="n">
-        <v>50880.702808</v>
+        <v>50881.34389</v>
       </c>
       <c r="H166" t="n">
-        <v>74745.98329800001</v>
+        <v>74747.873271</v>
       </c>
       <c r="I166" t="n">
-        <v>102697.858633</v>
+        <v>102704.5754</v>
       </c>
       <c r="J166" t="n">
         <v>34247.342751</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>50978.290535</v>
+        <v>50978.17201</v>
       </c>
       <c r="F167" t="n">
-        <v>54516.774702</v>
+        <v>54516.407324</v>
       </c>
       <c r="G167" t="n">
-        <v>74273.134051</v>
+        <v>74272.001978</v>
       </c>
       <c r="H167" t="n">
-        <v>110936.560868</v>
+        <v>110932.817477</v>
       </c>
       <c r="I167" t="n">
-        <v>159027.573586</v>
+        <v>159012.986204</v>
       </c>
       <c r="J167" t="n">
         <v>480732.503893</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>310.935792</v>
+        <v>310.935897</v>
       </c>
       <c r="F168" t="n">
-        <v>365.553875</v>
+        <v>365.553796</v>
       </c>
       <c r="G168" t="n">
-        <v>534.1229949999999</v>
+        <v>534.12181</v>
       </c>
       <c r="H168" t="n">
-        <v>823.8877199999999</v>
+        <v>823.8820940000001</v>
       </c>
       <c r="I168" t="n">
-        <v>1191.89013</v>
+        <v>1191.865514</v>
       </c>
       <c r="J168" t="n">
         <v>2182.254447</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>71417.175816</v>
+        <v>71417.294689</v>
       </c>
       <c r="F169" t="n">
-        <v>82850.503937</v>
+        <v>82850.794178</v>
       </c>
       <c r="G169" t="n">
-        <v>119236.74757</v>
+        <v>119237.472641</v>
       </c>
       <c r="H169" t="n">
-        <v>185764.6666</v>
+        <v>185766.731974</v>
       </c>
       <c r="I169" t="n">
-        <v>277920.440343</v>
+        <v>277927.798199</v>
       </c>
       <c r="J169" t="n">
         <v>302843.404518</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>8691.710432</v>
+        <v>8691.72855</v>
       </c>
       <c r="F170" t="n">
-        <v>12255.748149</v>
+        <v>12255.800233</v>
       </c>
       <c r="G170" t="n">
-        <v>20309.082734</v>
+        <v>20309.225349</v>
       </c>
       <c r="H170" t="n">
-        <v>33376.207188</v>
+        <v>33376.629125</v>
       </c>
       <c r="I170" t="n">
-        <v>49515.036489</v>
+        <v>49516.576039</v>
       </c>
       <c r="J170" t="n">
         <v>46489.459121</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>34194.924861</v>
+        <v>34194.953384</v>
       </c>
       <c r="F171" t="n">
-        <v>38220.978109</v>
+        <v>38221.022052</v>
       </c>
       <c r="G171" t="n">
-        <v>53199.576752</v>
+        <v>53199.618186</v>
       </c>
       <c r="H171" t="n">
-        <v>78092.606359</v>
+        <v>78092.580271</v>
       </c>
       <c r="I171" t="n">
-        <v>107352.191762</v>
+        <v>107351.84238</v>
       </c>
       <c r="J171" t="n">
         <v>156240.758755</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3150.518435</v>
+        <v>3150.012657</v>
       </c>
       <c r="F172" t="n">
-        <v>3310.11038</v>
+        <v>3308.70807</v>
       </c>
       <c r="G172" t="n">
-        <v>4186.895333</v>
+        <v>4183.261367</v>
       </c>
       <c r="H172" t="n">
-        <v>5671.039941</v>
+        <v>5661.088844</v>
       </c>
       <c r="I172" t="n">
-        <v>7521.986357</v>
+        <v>7488.865408</v>
       </c>
       <c r="J172" t="n">
         <v>514839.97731</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>692.174738</v>
+        <v>692.176559</v>
       </c>
       <c r="F173" t="n">
-        <v>936.439262</v>
+        <v>936.444856</v>
       </c>
       <c r="G173" t="n">
-        <v>1510.000557</v>
+        <v>1510.017401</v>
       </c>
       <c r="H173" t="n">
-        <v>2445.533829</v>
+        <v>2445.587597</v>
       </c>
       <c r="I173" t="n">
-        <v>3645.437548</v>
+        <v>3645.643111</v>
       </c>
       <c r="J173" t="n">
         <v>1881.916999</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>47818.291727</v>
+        <v>47818.037708</v>
       </c>
       <c r="F174" t="n">
-        <v>50948.876121</v>
+        <v>50948.106269</v>
       </c>
       <c r="G174" t="n">
-        <v>68080.445548</v>
+        <v>68078.15581500001</v>
       </c>
       <c r="H174" t="n">
-        <v>98398.051951</v>
+        <v>98390.815499</v>
       </c>
       <c r="I174" t="n">
-        <v>136079.640596</v>
+        <v>136052.570926</v>
       </c>
       <c r="J174" t="n">
         <v>657659.768187</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1429.399443</v>
+        <v>1429.403716</v>
       </c>
       <c r="F175" t="n">
-        <v>2352.46383</v>
+        <v>2352.480069</v>
       </c>
       <c r="G175" t="n">
-        <v>4630.324963</v>
+        <v>4630.384992</v>
       </c>
       <c r="H175" t="n">
-        <v>8917.318465</v>
+        <v>8917.543976000001</v>
       </c>
       <c r="I175" t="n">
-        <v>15282.732398</v>
+        <v>15283.704918</v>
       </c>
       <c r="J175" t="n">
         <v>7028.328485</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>122.271474</v>
+        <v>122.271322</v>
       </c>
       <c r="F176" t="n">
-        <v>123.266471</v>
+        <v>123.265993</v>
       </c>
       <c r="G176" t="n">
-        <v>160.037937</v>
+        <v>160.036453</v>
       </c>
       <c r="H176" t="n">
-        <v>226.765124</v>
+        <v>226.760366</v>
       </c>
       <c r="I176" t="n">
-        <v>307.814207</v>
+        <v>307.796585</v>
       </c>
       <c r="J176" t="n">
         <v>711.8727730000001</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>191968.837878</v>
+        <v>191969.311839</v>
       </c>
       <c r="F177" t="n">
-        <v>276281.379877</v>
+        <v>276282.84906</v>
       </c>
       <c r="G177" t="n">
-        <v>463063.122375</v>
+        <v>463067.432251</v>
       </c>
       <c r="H177" t="n">
-        <v>752489.778408</v>
+        <v>752502.891511</v>
       </c>
       <c r="I177" t="n">
-        <v>1079918.347021</v>
+        <v>1079965.587881</v>
       </c>
       <c r="J177" t="n">
         <v>743658.9253689999</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>306.924036</v>
+        <v>306.923843</v>
       </c>
       <c r="F178" t="n">
-        <v>380.355731</v>
+        <v>380.354567</v>
       </c>
       <c r="G178" t="n">
-        <v>569.805222</v>
+        <v>569.800382</v>
       </c>
       <c r="H178" t="n">
-        <v>893.050845</v>
+        <v>893.032788</v>
       </c>
       <c r="I178" t="n">
-        <v>1307.167675</v>
+        <v>1307.094713</v>
       </c>
       <c r="J178" t="n">
         <v>3197.147013</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>212.480694</v>
+        <v>212.480595</v>
       </c>
       <c r="F179" t="n">
-        <v>231.419628</v>
+        <v>231.419083</v>
       </c>
       <c r="G179" t="n">
-        <v>322.285088</v>
+        <v>322.282808</v>
       </c>
       <c r="H179" t="n">
-        <v>474.963312</v>
+        <v>474.954896</v>
       </c>
       <c r="I179" t="n">
-        <v>658.043106</v>
+        <v>658.009495</v>
       </c>
       <c r="J179" t="n">
         <v>1498.625284</v>
@@ -14130,19 +14130,19 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-2e-06</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="G181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="H181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="I181" t="n">
         <v>-4e-06</v>
-      </c>
-      <c r="G181" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="H181" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I181" t="n">
-        <v>-1e-06</v>
       </c>
       <c r="J181" t="n">
         <v>3e-06</v>
